--- a/files/option_more_steps.xlsx
+++ b/files/option_more_steps.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oyvind/Library/Mobile Documents/com~apple~CloudDocs/Documents/Teaching/SelFin_2023/S09_options/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oyvind/Projects/mst0037_files/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA50B16-EF7A-2A48-B1DB-4ACC6E12E287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D168B729-61F5-9148-BE89-F55C27441776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="1820" windowWidth="25940" windowHeight="14920" activeTab="1" xr2:uid="{60177B54-9B19-F545-8921-37B5D693AC6D}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Price" sheetId="4" r:id="rId1"/>
     <sheet name="Option" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -337,8 +337,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="167" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -527,7 +527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -538,11 +538,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
@@ -551,8 +547,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -562,9 +558,9 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1913,9 +1909,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1953,7 +1949,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2059,7 +2055,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2201,7 +2197,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2232,16 +2228,16 @@
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="K4" s="19">
+      <c r="K4" s="17">
         <f>I6*$C$6</f>
         <v>73.649159107599985</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="11">
         <v>50</v>
       </c>
       <c r="I5" s="3" t="s">
@@ -2249,13 +2245,13 @@
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="13">
         <v>1.1377999999999999</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="16">
         <f>G8*$C$6</f>
         <v>64.729441999999992</v>
       </c>
@@ -2270,19 +2266,19 @@
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="15">
         <f>1/C6</f>
         <v>0.87888908419757428</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="16">
         <f>E10*$C$6</f>
         <v>56.889999999999993</v>
       </c>
       <c r="H8" s="2"/>
-      <c r="K8" s="19">
+      <c r="K8" s="17">
         <f>I6*$C$8</f>
         <v>56.889999999999993</v>
       </c>
@@ -2301,7 +2297,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="I10" s="18">
+      <c r="I10" s="16">
         <f>G8*$C$8</f>
         <v>49.999999999999993</v>
       </c>
@@ -2316,12 +2312,12 @@
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="G12" s="18">
+      <c r="G12" s="16">
         <f>E10*$C$8</f>
         <v>43.944454209878714</v>
       </c>
       <c r="H12" s="2"/>
-      <c r="K12" s="19">
+      <c r="K12" s="17">
         <f>I10*$C$8</f>
         <v>43.944454209878707</v>
       </c>
@@ -2332,7 +2328,7 @@
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="I14" s="18">
+      <c r="I14" s="16">
         <f>G12*$C$8</f>
         <v>38.622301116082539</v>
       </c>
@@ -2344,7 +2340,7 @@
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="K16" s="19">
+      <c r="K16" s="17">
         <f>I14*$C$8</f>
         <v>33.944718857516733</v>
       </c>
@@ -2377,12 +2373,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="M2" s="20" t="s">
+      <c r="M2" s="18" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="M3" s="21" t="s">
+      <c r="M3" s="19" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2393,71 +2389,67 @@
       <c r="M4" s="4"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="K5" s="19">
+      <c r="K5" s="17">
         <f>MAX(0,Price!K4-Option!$C$7)</f>
         <v>28.649159107599985</v>
       </c>
-      <c r="M5" s="25">
+      <c r="M5" s="23">
         <f>C13^3</f>
         <v>0.1155942697088839</v>
       </c>
     </row>
     <row r="6" spans="2:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="11">
         <v>50</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="6"/>
-      <c r="M6" s="8"/>
+      <c r="M6" s="6"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="21">
         <v>45</v>
       </c>
-      <c r="I7" s="18"/>
-      <c r="J7" s="7"/>
-      <c r="M7" s="8"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="2"/>
+      <c r="M7" s="6"/>
     </row>
     <row r="8" spans="2:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="21">
         <v>1.1377999999999999</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="6"/>
       <c r="K8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="M8" s="26"/>
+      <c r="M8" s="24"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="13">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="7"/>
-      <c r="K9" s="19">
+      <c r="G9" s="16"/>
+      <c r="H9" s="2"/>
+      <c r="K9" s="17">
         <f>MAX(0,Price!K8-Option!$C$7)</f>
         <v>11.889999999999993</v>
       </c>
-      <c r="M9" s="25">
+      <c r="M9" s="23">
         <f>3*(1-C13)*C13^2</f>
         <v>0.36510593313987039</v>
       </c>
@@ -2466,55 +2458,52 @@
       <c r="E10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="6"/>
       <c r="I10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="6"/>
-      <c r="M10" s="8"/>
+      <c r="M10" s="6"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="E11" s="19">
+      <c r="E11" s="17">
         <f>(M5*K5+M9*K9+M13*K13+M17*K17)*EXP(-1*C9)</f>
         <v>7.5388529973720066</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="7"/>
-      <c r="M11" s="8"/>
+      <c r="F11" s="2"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="2"/>
+      <c r="M11" s="6"/>
     </row>
     <row r="12" spans="2:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="22">
         <f>1/C8</f>
         <v>0.87888908419757428</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="6"/>
       <c r="K12" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M12" s="4"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="9">
         <f>(EXP(C9/3)-C12)/(C8-C12)</f>
         <v>0.48713062665179863</v>
       </c>
-      <c r="G13" s="18"/>
-      <c r="H13" s="7"/>
-      <c r="K13" s="19">
+      <c r="G13" s="16"/>
+      <c r="H13" s="2"/>
+      <c r="K13" s="17">
         <f>MAX(0,Price!K12-Option!$C$7)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="25">
+      <c r="M13" s="23">
         <f>3*(1-C13)^2*C13</f>
         <v>0.38439720454900345</v>
       </c>
@@ -2523,13 +2512,12 @@
       <c r="I14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J14" s="6"/>
-      <c r="M14" s="8"/>
+      <c r="M14" s="6"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="I15" s="18"/>
-      <c r="J15" s="7"/>
-      <c r="M15" s="8"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="2"/>
+      <c r="M15" s="6"/>
     </row>
     <row r="16" spans="2:13" ht="18" x14ac:dyDescent="0.25">
       <c r="K16" s="3" t="s">
@@ -2538,20 +2526,20 @@
       <c r="M16" s="4"/>
     </row>
     <row r="17" spans="11:13" x14ac:dyDescent="0.2">
-      <c r="K17" s="19">
+      <c r="K17" s="17">
         <f>MAX(0,Price!K16-Option!$C$7)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="25">
+      <c r="M17" s="23">
         <f>(1-C13)^3</f>
         <v>0.1349025926022423</v>
       </c>
     </row>
     <row r="18" spans="11:13" x14ac:dyDescent="0.2">
-      <c r="M18" s="8"/>
+      <c r="M18" s="6"/>
     </row>
     <row r="19" spans="11:13" x14ac:dyDescent="0.2">
-      <c r="M19" s="8">
+      <c r="M19" s="6">
         <f>SUM(M5:M17)</f>
         <v>1</v>
       </c>
@@ -2561,4 +2549,10 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{9641a79b-5684-4ff8-89b0-3b715ae642f9}" enabled="1" method="Privileged" siteId="{adee44b2-91fc-40f1-abdd-9cc29351b5fd}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>